--- a/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
+++ b/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61CFE632-6A5B-496A-9F47-7D13B679B109}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -491,44 +489,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F52D849-8006-48A0-8D6B-88427B4C70FA}">
   <dimension ref="A1:AI31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" customWidth="1"/>
-    <col min="5" max="5" width="22.36328125" customWidth="1"/>
-    <col min="6" max="6" width="14.90625" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" customWidth="1"/>
-    <col min="8" max="8" width="19.26953125" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" customWidth="1"/>
-    <col min="10" max="10" width="12.08984375" customWidth="1"/>
-    <col min="11" max="11" width="19.1796875" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" customWidth="1"/>
-    <col min="13" max="13" width="10.90625" customWidth="1"/>
-    <col min="14" max="14" width="19.1796875" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" customWidth="1"/>
-    <col min="17" max="17" width="18.81640625" customWidth="1"/>
-    <col min="18" max="18" width="12.6328125" customWidth="1"/>
-    <col min="19" max="19" width="10.6328125" customWidth="1"/>
-    <col min="20" max="20" width="18.90625" customWidth="1"/>
-    <col min="21" max="21" width="12.6328125" customWidth="1"/>
-    <col min="22" max="22" width="10.54296875" customWidth="1"/>
-    <col min="23" max="23" width="17.90625" customWidth="1"/>
-    <col min="24" max="24" width="12.453125" customWidth="1"/>
-    <col min="25" max="25" width="11.90625" customWidth="1"/>
-    <col min="26" max="26" width="18.453125" customWidth="1"/>
-    <col min="27" max="27" width="13.08984375" customWidth="1"/>
-    <col min="28" max="28" width="11.08984375" customWidth="1"/>
-    <col min="29" max="29" width="18.08984375" customWidth="1"/>
-    <col min="30" max="30" width="12.90625" customWidth="1"/>
-    <col min="31" max="31" width="10.81640625" customWidth="1"/>
-    <col min="32" max="32" width="18.453125" customWidth="1"/>
-    <col min="33" max="33" width="13.54296875" customWidth="1"/>
-    <col min="34" max="34" width="10.90625" customWidth="1"/>
-    <col min="35" max="35" width="18.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" customWidth="1"/>
+    <col min="11" max="11" width="19.21875" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" customWidth="1"/>
+    <col min="13" max="13" width="10.88671875" customWidth="1"/>
+    <col min="14" max="14" width="19.21875" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" customWidth="1"/>
+    <col min="17" max="17" width="18.77734375" customWidth="1"/>
+    <col min="18" max="18" width="12.6640625" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" customWidth="1"/>
+    <col min="20" max="20" width="18.88671875" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" customWidth="1"/>
+    <col min="22" max="22" width="10.5546875" customWidth="1"/>
+    <col min="23" max="23" width="17.88671875" customWidth="1"/>
+    <col min="24" max="24" width="12.44140625" customWidth="1"/>
+    <col min="25" max="25" width="11.88671875" customWidth="1"/>
+    <col min="26" max="26" width="18.44140625" customWidth="1"/>
+    <col min="27" max="27" width="13.109375" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" customWidth="1"/>
+    <col min="29" max="29" width="18.109375" customWidth="1"/>
+    <col min="30" max="30" width="12.88671875" customWidth="1"/>
+    <col min="31" max="31" width="10.77734375" customWidth="1"/>
+    <col min="32" max="32" width="18.44140625" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" customWidth="1"/>
+    <col min="34" max="34" width="10.88671875" customWidth="1"/>
+    <col min="35" max="35" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
@@ -585,13 +589,9 @@
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
       <c r="C2" t="s">
         <v>4</v>
       </c>
@@ -611,7 +611,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J2" t="s">
         <v>3</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -799,7 +799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -906,7 +906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1663,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="G12">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1672,7 +1672,7 @@
         <v>4</v>
       </c>
       <c r="J12">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -1681,7 +1681,7 @@
         <v>4</v>
       </c>
       <c r="M12">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N12">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         <v>4</v>
       </c>
       <c r="P12">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Q12">
         <v>2</v>
@@ -1717,7 +1717,7 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z12">
         <v>3</v>
@@ -1726,7 +1726,7 @@
         <v>3</v>
       </c>
       <c r="AB12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AC12">
         <v>3</v>
@@ -1735,7 +1735,7 @@
         <v>3</v>
       </c>
       <c r="AE12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF12">
         <v>3</v>
@@ -1744,13 +1744,13 @@
         <v>3</v>
       </c>
       <c r="AH12">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AI12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>4</v>
       </c>
       <c r="D13">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1770,7 +1770,7 @@
         <v>4</v>
       </c>
       <c r="G13">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -1779,7 +1779,7 @@
         <v>4</v>
       </c>
       <c r="J13">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -1788,7 +1788,7 @@
         <v>4</v>
       </c>
       <c r="M13">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -1797,7 +1797,7 @@
         <v>4</v>
       </c>
       <c r="P13">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q13">
         <v>2</v>
@@ -1806,7 +1806,7 @@
         <v>4</v>
       </c>
       <c r="S13">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="T13">
         <v>2</v>
@@ -1815,7 +1815,7 @@
         <v>4</v>
       </c>
       <c r="V13">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="W13">
         <v>2</v>
@@ -1824,7 +1824,7 @@
         <v>2</v>
       </c>
       <c r="Y13">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Z13">
         <v>2</v>
@@ -1833,7 +1833,7 @@
         <v>2</v>
       </c>
       <c r="AB13">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AC13">
         <v>2</v>
@@ -1842,7 +1842,7 @@
         <v>2</v>
       </c>
       <c r="AE13">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AF13">
         <v>2</v>
@@ -1857,7 +1857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>4</v>
       </c>
       <c r="S14">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="T14">
         <v>4</v>
@@ -1922,7 +1922,7 @@
         <v>4</v>
       </c>
       <c r="V14">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="W14">
         <v>4</v>
@@ -1931,7 +1931,7 @@
         <v>3</v>
       </c>
       <c r="Y14">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="Z14">
         <v>3</v>
@@ -1940,7 +1940,7 @@
         <v>3</v>
       </c>
       <c r="AB14">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="AC14">
         <v>3</v>
@@ -1949,7 +1949,7 @@
         <v>3</v>
       </c>
       <c r="AE14">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="AF14">
         <v>3</v>
@@ -1958,13 +1958,13 @@
         <v>3</v>
       </c>
       <c r="AH14">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="AI14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2071,7 +2071,120 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>59</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>59</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>59</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>59</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>2</v>
+      </c>
+      <c r="P16">
+        <v>59</v>
+      </c>
+      <c r="Q16">
+        <v>2</v>
+      </c>
+      <c r="R16">
+        <v>2</v>
+      </c>
+      <c r="S16">
+        <v>59</v>
+      </c>
+      <c r="T16">
+        <v>2</v>
+      </c>
+      <c r="U16">
+        <v>2</v>
+      </c>
+      <c r="V16">
+        <v>59</v>
+      </c>
+      <c r="W16">
+        <v>2</v>
+      </c>
+      <c r="X16">
+        <v>2</v>
+      </c>
+      <c r="Y16">
+        <v>59</v>
+      </c>
+      <c r="Z16">
+        <v>2</v>
+      </c>
+      <c r="AA16">
+        <v>2</v>
+      </c>
+      <c r="AB16">
+        <v>59</v>
+      </c>
+      <c r="AC16">
+        <v>2</v>
+      </c>
+      <c r="AD16">
+        <v>2</v>
+      </c>
+      <c r="AE16">
+        <v>59</v>
+      </c>
+      <c r="AF16">
+        <v>2</v>
+      </c>
+      <c r="AG16">
+        <v>2</v>
+      </c>
+      <c r="AH16">
+        <v>59</v>
+      </c>
+      <c r="AI16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="C20" s="3" t="s">
         <v>2</v>
       </c>
@@ -2108,13 +2221,9 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1</v>
-      </c>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
       <c r="C21" t="s">
         <v>7</v>
       </c>
@@ -2179,7 +2288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2250,7 +2359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2321,7 +2430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2392,7 +2501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2463,7 +2572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2534,7 +2643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2605,7 +2714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2676,7 +2785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2747,7 +2856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2818,7 +2927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2884,12 +2993,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="X1:Z1"/>
+  <mergeCells count="22">
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="AD1:AF1"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="U20:W20"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="X1:Z1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="F20:H20"/>
@@ -2901,8 +3016,6 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="U1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
+++ b/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61CFE632-6A5B-496A-9F47-7D13B679B109}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEBE76A0-5815-463A-9A65-F8292CB4141D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
   </bookViews>
@@ -2344,7 +2344,7 @@
         <v>4</v>
       </c>
       <c r="S22">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="T22">
         <v>2</v>
@@ -2353,7 +2353,7 @@
         <v>4</v>
       </c>
       <c r="V22">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W22">
         <v>2</v>
@@ -2415,7 +2415,7 @@
         <v>4</v>
       </c>
       <c r="S23">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="T23">
         <v>2</v>
@@ -2424,7 +2424,7 @@
         <v>4</v>
       </c>
       <c r="V23">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="W23">
         <v>2</v>
@@ -2994,12 +2994,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="U1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A20:A21"/>
@@ -3016,6 +3010,12 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="U1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
+++ b/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEBE76A0-5815-463A-9A65-F8292CB4141D}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C1ED10E-F165-4903-B0B3-A701725BA0F0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2817,7 +2817,7 @@
         <v>45</v>
       </c>
       <c r="K29">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -2994,6 +2994,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="U1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A20:A21"/>
@@ -3010,12 +3016,6 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="U1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
+++ b/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C1ED10E-F165-4903-B0B3-A701725BA0F0}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3918B7-38D6-4666-B46C-F30B2F1499DE}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -165,10 +165,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1654,7 +1650,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1663,7 +1659,7 @@
         <v>4</v>
       </c>
       <c r="G12">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1672,7 +1668,7 @@
         <v>4</v>
       </c>
       <c r="J12">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -1681,7 +1677,7 @@
         <v>4</v>
       </c>
       <c r="M12">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="N12">
         <v>2</v>
@@ -1690,7 +1686,7 @@
         <v>4</v>
       </c>
       <c r="P12">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q12">
         <v>2</v>
@@ -1699,7 +1695,7 @@
         <v>4</v>
       </c>
       <c r="S12">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="T12">
         <v>2</v>
@@ -1708,7 +1704,7 @@
         <v>4</v>
       </c>
       <c r="V12">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="W12">
         <v>2</v>
@@ -1717,7 +1713,7 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="Z12">
         <v>3</v>
@@ -1726,7 +1722,7 @@
         <v>3</v>
       </c>
       <c r="AB12">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AC12">
         <v>3</v>
@@ -1735,7 +1731,7 @@
         <v>3</v>
       </c>
       <c r="AE12">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AF12">
         <v>3</v>
@@ -1744,7 +1740,7 @@
         <v>3</v>
       </c>
       <c r="AH12">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="AI12">
         <v>3</v>
@@ -1761,7 +1757,7 @@
         <v>4</v>
       </c>
       <c r="D13">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1770,7 +1766,7 @@
         <v>4</v>
       </c>
       <c r="G13">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -1779,7 +1775,7 @@
         <v>4</v>
       </c>
       <c r="J13">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -1788,7 +1784,7 @@
         <v>4</v>
       </c>
       <c r="M13">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -1797,7 +1793,7 @@
         <v>4</v>
       </c>
       <c r="P13">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="Q13">
         <v>2</v>
@@ -1806,7 +1802,7 @@
         <v>4</v>
       </c>
       <c r="S13">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="T13">
         <v>2</v>
@@ -1815,7 +1811,7 @@
         <v>4</v>
       </c>
       <c r="V13">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="W13">
         <v>2</v>
@@ -1824,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="Y13">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="Z13">
         <v>2</v>
@@ -1833,7 +1829,7 @@
         <v>2</v>
       </c>
       <c r="AB13">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="AC13">
         <v>2</v>
@@ -1842,7 +1838,7 @@
         <v>2</v>
       </c>
       <c r="AE13">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AF13">
         <v>2</v>
@@ -1851,7 +1847,7 @@
         <v>2</v>
       </c>
       <c r="AH13">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="AI13">
         <v>2</v>
@@ -1877,7 +1873,7 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -1886,7 +1882,7 @@
         <v>4</v>
       </c>
       <c r="J14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K14">
         <v>4</v>
@@ -1895,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="M14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N14">
         <v>4</v>
@@ -1904,7 +1900,7 @@
         <v>4</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -1913,7 +1909,7 @@
         <v>4</v>
       </c>
       <c r="S14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="T14">
         <v>4</v>
@@ -1922,7 +1918,7 @@
         <v>4</v>
       </c>
       <c r="V14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="W14">
         <v>4</v>
@@ -1931,7 +1927,7 @@
         <v>3</v>
       </c>
       <c r="Y14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Z14">
         <v>3</v>
@@ -1940,7 +1936,7 @@
         <v>3</v>
       </c>
       <c r="AB14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AC14">
         <v>3</v>
@@ -1949,7 +1945,7 @@
         <v>3</v>
       </c>
       <c r="AE14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AF14">
         <v>3</v>
@@ -1958,7 +1954,7 @@
         <v>3</v>
       </c>
       <c r="AH14">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AI14">
         <v>3</v>
@@ -2082,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="D16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -2091,7 +2087,7 @@
         <v>2</v>
       </c>
       <c r="G16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -2100,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="J16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K16">
         <v>2</v>
@@ -2109,7 +2105,7 @@
         <v>2</v>
       </c>
       <c r="M16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="N16">
         <v>2</v>
@@ -2118,7 +2114,7 @@
         <v>2</v>
       </c>
       <c r="P16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -2127,7 +2123,7 @@
         <v>2</v>
       </c>
       <c r="S16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="T16">
         <v>2</v>
@@ -2136,7 +2132,7 @@
         <v>2</v>
       </c>
       <c r="V16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="W16">
         <v>2</v>
@@ -2145,7 +2141,7 @@
         <v>2</v>
       </c>
       <c r="Y16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="Z16">
         <v>2</v>
@@ -2154,7 +2150,7 @@
         <v>2</v>
       </c>
       <c r="AB16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="AC16">
         <v>2</v>
@@ -2163,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="AE16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="AF16">
         <v>2</v>
@@ -2172,7 +2168,7 @@
         <v>2</v>
       </c>
       <c r="AH16">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="AI16">
         <v>2</v>
@@ -2344,7 +2340,7 @@
         <v>4</v>
       </c>
       <c r="S22">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="T22">
         <v>2</v>
@@ -2353,7 +2349,7 @@
         <v>4</v>
       </c>
       <c r="V22">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="W22">
         <v>2</v>
@@ -2415,7 +2411,7 @@
         <v>4</v>
       </c>
       <c r="S23">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="T23">
         <v>2</v>
@@ -2424,7 +2420,7 @@
         <v>4</v>
       </c>
       <c r="V23">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="W23">
         <v>2</v>
@@ -2994,12 +2990,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="U1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A20:A21"/>
@@ -3016,6 +3006,12 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="U1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
+++ b/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{9A05B8BF-6FFD-4A62-AA37-CF25288AF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3918B7-38D6-4666-B46C-F30B2F1499DE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2918608-FAE1-48A9-97E2-3325D22D4987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="19">
   <si>
     <t>YEAR</t>
   </si>
@@ -60,13 +60,7 @@
     <t xml:space="preserve">NO OF HOURS </t>
   </si>
   <si>
-    <t>38,11</t>
-  </si>
-  <si>
     <t>C3</t>
-  </si>
-  <si>
-    <t>11,31</t>
   </si>
   <si>
     <t>C4</t>
@@ -81,15 +75,6 @@
     <t>C7</t>
   </si>
   <si>
-    <t>7,11</t>
-  </si>
-  <si>
-    <t>11,38</t>
-  </si>
-  <si>
-    <t>31,11</t>
-  </si>
-  <si>
     <t>G1</t>
   </si>
   <si>
@@ -102,10 +87,10 @@
     <t>G4</t>
   </si>
   <si>
-    <t>11,7</t>
+    <t xml:space="preserve">FACULTY-ID </t>
   </si>
   <si>
-    <t xml:space="preserve">FACULTY-ID </t>
+    <t>16,25</t>
   </si>
 </sst>
 </file>
@@ -141,12 +126,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -484,110 +468,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F52D849-8006-48A0-8D6B-88427B4C70FA}">
-  <dimension ref="A1:AI31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AI29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" customWidth="1"/>
-    <col min="8" max="8" width="19.21875" customWidth="1"/>
-    <col min="9" max="9" width="15.21875" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" customWidth="1"/>
-    <col min="11" max="11" width="19.21875" customWidth="1"/>
-    <col min="12" max="12" width="14.21875" customWidth="1"/>
-    <col min="13" max="13" width="10.88671875" customWidth="1"/>
-    <col min="14" max="14" width="19.21875" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" customWidth="1"/>
-    <col min="16" max="16" width="10.88671875" customWidth="1"/>
-    <col min="17" max="17" width="18.77734375" customWidth="1"/>
-    <col min="18" max="18" width="12.6640625" customWidth="1"/>
-    <col min="19" max="19" width="10.6640625" customWidth="1"/>
-    <col min="20" max="20" width="18.88671875" customWidth="1"/>
-    <col min="21" max="21" width="12.6640625" customWidth="1"/>
-    <col min="22" max="22" width="10.5546875" customWidth="1"/>
-    <col min="23" max="23" width="17.88671875" customWidth="1"/>
-    <col min="24" max="24" width="12.44140625" customWidth="1"/>
-    <col min="25" max="25" width="11.88671875" customWidth="1"/>
-    <col min="26" max="26" width="18.44140625" customWidth="1"/>
-    <col min="27" max="27" width="13.109375" customWidth="1"/>
-    <col min="28" max="28" width="11.109375" customWidth="1"/>
-    <col min="29" max="29" width="18.109375" customWidth="1"/>
-    <col min="30" max="30" width="12.88671875" customWidth="1"/>
-    <col min="31" max="31" width="10.77734375" customWidth="1"/>
-    <col min="32" max="32" width="18.44140625" customWidth="1"/>
-    <col min="33" max="33" width="13.5546875" customWidth="1"/>
-    <col min="34" max="34" width="10.88671875" customWidth="1"/>
-    <col min="35" max="35" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" customWidth="1"/>
+    <col min="5" max="5" width="22.36328125" customWidth="1"/>
+    <col min="6" max="6" width="14.90625" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" customWidth="1"/>
+    <col min="8" max="8" width="19.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.1796875" customWidth="1"/>
+    <col min="10" max="10" width="12.08984375" customWidth="1"/>
+    <col min="11" max="11" width="19.1796875" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" customWidth="1"/>
+    <col min="13" max="13" width="10.90625" customWidth="1"/>
+    <col min="14" max="14" width="19.1796875" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" customWidth="1"/>
+    <col min="16" max="16" width="10.90625" customWidth="1"/>
+    <col min="17" max="17" width="18.81640625" customWidth="1"/>
+    <col min="18" max="18" width="12.6328125" customWidth="1"/>
+    <col min="19" max="19" width="10.6328125" customWidth="1"/>
+    <col min="20" max="20" width="18.90625" customWidth="1"/>
+    <col min="21" max="21" width="12.6328125" customWidth="1"/>
+    <col min="22" max="22" width="10.54296875" customWidth="1"/>
+    <col min="23" max="23" width="17.90625" customWidth="1"/>
+    <col min="24" max="24" width="12.453125" customWidth="1"/>
+    <col min="25" max="25" width="11.90625" customWidth="1"/>
+    <col min="26" max="26" width="18.453125" customWidth="1"/>
+    <col min="27" max="27" width="13.08984375" customWidth="1"/>
+    <col min="28" max="28" width="11.08984375" customWidth="1"/>
+    <col min="29" max="29" width="18.08984375" customWidth="1"/>
+    <col min="30" max="30" width="12.90625" customWidth="1"/>
+    <col min="31" max="31" width="10.81640625" customWidth="1"/>
+    <col min="32" max="32" width="18.453125" customWidth="1"/>
+    <col min="33" max="33" width="13.54296875" customWidth="1"/>
+    <col min="34" max="34" width="10.90625" customWidth="1"/>
+    <col min="35" max="35" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3" t="s">
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3" t="s">
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3" t="s">
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
       <c r="C2" t="s">
         <v>4</v>
       </c>
@@ -688,7 +672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -696,7 +680,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -705,7 +689,7 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -714,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -723,7 +707,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -732,7 +716,7 @@
         <v>2</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P3">
         <v>39</v>
@@ -741,7 +725,7 @@
         <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S3">
         <v>39</v>
@@ -750,7 +734,7 @@
         <v>2</v>
       </c>
       <c r="U3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V3">
         <v>39</v>
@@ -759,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="X3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y3">
         <v>6</v>
@@ -768,7 +752,7 @@
         <v>2</v>
       </c>
       <c r="AA3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB3">
         <v>6</v>
@@ -777,7 +761,7 @@
         <v>2</v>
       </c>
       <c r="AD3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE3">
         <v>5</v>
@@ -786,7 +770,7 @@
         <v>2</v>
       </c>
       <c r="AG3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH3">
         <v>20</v>
@@ -795,7 +779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -803,7 +787,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>40</v>
@@ -812,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>40</v>
@@ -821,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>19</v>
@@ -830,7 +814,7 @@
         <v>2</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>19</v>
@@ -839,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>40</v>
@@ -848,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="R4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>27</v>
@@ -857,7 +841,7 @@
         <v>2</v>
       </c>
       <c r="U4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>27</v>
@@ -866,7 +850,7 @@
         <v>2</v>
       </c>
       <c r="X4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>27</v>
@@ -875,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="AA4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>40</v>
@@ -884,7 +868,7 @@
         <v>2</v>
       </c>
       <c r="AD4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE4">
         <v>34</v>
@@ -893,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="AG4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH4">
         <v>19</v>
@@ -902,7 +886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -910,7 +894,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -919,7 +903,7 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -928,7 +912,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -937,7 +921,7 @@
         <v>2</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>29</v>
@@ -946,7 +930,7 @@
         <v>2</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>13</v>
@@ -955,7 +939,7 @@
         <v>2</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>33</v>
@@ -964,7 +948,7 @@
         <v>2</v>
       </c>
       <c r="U5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -973,7 +957,7 @@
         <v>2</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>35</v>
@@ -982,7 +966,7 @@
         <v>2</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>13</v>
@@ -991,7 +975,7 @@
         <v>2</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5">
         <v>35</v>
@@ -1000,7 +984,7 @@
         <v>2</v>
       </c>
       <c r="AG5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH5">
         <v>12</v>
@@ -1009,7 +993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1017,7 +1001,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -1026,7 +1010,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>38</v>
@@ -1035,7 +1019,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1044,7 +1028,7 @@
         <v>2</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -1053,7 +1037,7 @@
         <v>2</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>28</v>
@@ -1062,7 +1046,7 @@
         <v>2</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>7</v>
@@ -1071,7 +1055,7 @@
         <v>2</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>31</v>
@@ -1080,7 +1064,7 @@
         <v>2</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>28</v>
@@ -1089,7 +1073,7 @@
         <v>2</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -1098,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="AD6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE6">
         <v>38</v>
@@ -1107,7 +1091,7 @@
         <v>2</v>
       </c>
       <c r="AG6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH6">
         <v>31</v>
@@ -1116,7 +1100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1124,7 +1108,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -1133,55 +1117,55 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>38</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
       </c>
       <c r="N7">
         <v>1</v>
       </c>
       <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>38</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7" t="s">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="S7">
+        <v>11</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
       <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>11</v>
       </c>
       <c r="W7">
         <v>1</v>
@@ -1198,8 +1182,8 @@
       <c r="AA7">
         <v>2</v>
       </c>
-      <c r="AB7" t="s">
-        <v>22</v>
+      <c r="AB7">
+        <v>17</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -1207,8 +1191,8 @@
       <c r="AD7">
         <v>2</v>
       </c>
-      <c r="AE7" t="s">
-        <v>16</v>
+      <c r="AE7">
+        <v>38</v>
       </c>
       <c r="AF7">
         <v>2</v>
@@ -1216,14 +1200,14 @@
       <c r="AG7">
         <v>2</v>
       </c>
-      <c r="AH7" t="s">
-        <v>10</v>
+      <c r="AH7">
+        <v>31</v>
       </c>
       <c r="AI7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1318,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1425,7 +1409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1532,7 +1516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1639,663 +1623,555 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>15</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>32</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <v>5</v>
+      </c>
+      <c r="M12">
+        <v>15</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>5</v>
+      </c>
+      <c r="P12">
+        <v>32</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
+      </c>
+      <c r="R12">
+        <v>5</v>
+      </c>
+      <c r="S12">
+        <v>15</v>
+      </c>
+      <c r="T12">
+        <v>2</v>
+      </c>
+      <c r="U12">
+        <v>5</v>
+      </c>
+      <c r="V12">
+        <v>15</v>
+      </c>
+      <c r="W12">
+        <v>2</v>
+      </c>
+      <c r="X12">
+        <v>6</v>
+      </c>
+      <c r="Y12">
+        <v>32</v>
+      </c>
+      <c r="Z12">
+        <v>2</v>
+      </c>
+      <c r="AA12">
+        <v>6</v>
+      </c>
+      <c r="AB12">
+        <v>32</v>
+      </c>
+      <c r="AC12">
+        <v>2</v>
+      </c>
+      <c r="AD12">
+        <v>6</v>
+      </c>
+      <c r="AE12">
+        <v>32</v>
+      </c>
+      <c r="AF12">
+        <v>4</v>
+      </c>
+      <c r="AG12">
+        <v>6</v>
+      </c>
+      <c r="AH12">
+        <v>15</v>
+      </c>
+      <c r="AI12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>82</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>82</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>82</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>82</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>82</v>
+      </c>
+      <c r="Q13">
+        <v>2</v>
+      </c>
+      <c r="R13">
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <v>82</v>
+      </c>
+      <c r="T13">
+        <v>2</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>82</v>
+      </c>
+      <c r="W13">
+        <v>2</v>
+      </c>
+      <c r="X13">
+        <v>2</v>
+      </c>
+      <c r="Y13">
+        <v>82</v>
+      </c>
+      <c r="Z13">
+        <v>2</v>
+      </c>
+      <c r="AA13">
+        <v>2</v>
+      </c>
+      <c r="AB13">
+        <v>82</v>
+      </c>
+      <c r="AC13">
+        <v>2</v>
+      </c>
+      <c r="AD13">
+        <v>2</v>
+      </c>
+      <c r="AE13">
+        <v>82</v>
+      </c>
+      <c r="AF13">
+        <v>2</v>
+      </c>
+      <c r="AG13">
+        <v>2</v>
+      </c>
+      <c r="AH13">
+        <v>82</v>
+      </c>
+      <c r="AI13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" t="s">
+        <v>7</v>
+      </c>
+      <c r="S18" t="s">
+        <v>17</v>
+      </c>
+      <c r="T18" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>26</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>36</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>26</v>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <v>5</v>
+      </c>
+      <c r="M19">
+        <v>36</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19">
+        <v>5</v>
+      </c>
+      <c r="P19">
+        <v>36</v>
+      </c>
+      <c r="Q19">
+        <v>2</v>
+      </c>
+      <c r="R19">
+        <v>6</v>
+      </c>
+      <c r="S19">
+        <v>26</v>
+      </c>
+      <c r="T19">
+        <v>2</v>
+      </c>
+      <c r="U19">
+        <v>6</v>
+      </c>
+      <c r="V19">
+        <v>36</v>
+      </c>
+      <c r="W19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
         <v>11</v>
       </c>
-      <c r="C12">
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>33</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>41</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>14</v>
+      </c>
+      <c r="K20">
         <v>4</v>
       </c>
-      <c r="D12">
-        <v>71</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
+      <c r="L20">
+        <v>5</v>
+      </c>
+      <c r="M20">
+        <v>16</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+      <c r="O20">
+        <v>5</v>
+      </c>
+      <c r="P20">
+        <v>14</v>
+      </c>
+      <c r="Q20">
+        <v>2</v>
+      </c>
+      <c r="R20">
+        <v>5</v>
+      </c>
+      <c r="S20">
+        <v>41</v>
+      </c>
+      <c r="T20">
+        <v>2</v>
+      </c>
+      <c r="U20">
+        <v>5</v>
+      </c>
+      <c r="V20">
+        <v>16</v>
+      </c>
+      <c r="W20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>17</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>17</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>17</v>
+      </c>
+      <c r="K21">
         <v>4</v>
       </c>
-      <c r="G12">
-        <v>72</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-      <c r="I12">
-        <v>4</v>
-      </c>
-      <c r="J12">
-        <v>73</v>
-      </c>
-      <c r="K12">
-        <v>2</v>
-      </c>
-      <c r="L12">
-        <v>4</v>
-      </c>
-      <c r="M12">
-        <v>74</v>
-      </c>
-      <c r="N12">
-        <v>2</v>
-      </c>
-      <c r="O12">
-        <v>4</v>
-      </c>
-      <c r="P12">
-        <v>75</v>
-      </c>
-      <c r="Q12">
-        <v>2</v>
-      </c>
-      <c r="R12">
-        <v>4</v>
-      </c>
-      <c r="S12">
-        <v>76</v>
-      </c>
-      <c r="T12">
-        <v>2</v>
-      </c>
-      <c r="U12">
-        <v>4</v>
-      </c>
-      <c r="V12">
-        <v>77</v>
-      </c>
-      <c r="W12">
-        <v>2</v>
-      </c>
-      <c r="X12">
-        <v>3</v>
-      </c>
-      <c r="Y12">
-        <v>78</v>
-      </c>
-      <c r="Z12">
-        <v>3</v>
-      </c>
-      <c r="AA12">
-        <v>3</v>
-      </c>
-      <c r="AB12">
-        <v>79</v>
-      </c>
-      <c r="AC12">
-        <v>3</v>
-      </c>
-      <c r="AD12">
-        <v>3</v>
-      </c>
-      <c r="AE12">
-        <v>80</v>
-      </c>
-      <c r="AF12">
-        <v>3</v>
-      </c>
-      <c r="AG12">
-        <v>3</v>
-      </c>
-      <c r="AH12">
-        <v>81</v>
-      </c>
-      <c r="AI12">
-        <v>3</v>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>24</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21">
+        <v>5</v>
+      </c>
+      <c r="P21">
+        <v>37</v>
+      </c>
+      <c r="Q21">
+        <v>2</v>
+      </c>
+      <c r="R21">
+        <v>5</v>
+      </c>
+      <c r="S21">
+        <v>24</v>
+      </c>
+      <c r="T21">
+        <v>2</v>
+      </c>
+      <c r="U21">
+        <v>5</v>
+      </c>
+      <c r="V21">
+        <v>37</v>
+      </c>
+      <c r="W21">
+        <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>60</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>4</v>
-      </c>
-      <c r="G13">
-        <v>61</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <v>4</v>
-      </c>
-      <c r="J13">
-        <v>62</v>
-      </c>
-      <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13">
-        <v>4</v>
-      </c>
-      <c r="M13">
-        <v>63</v>
-      </c>
-      <c r="N13">
-        <v>2</v>
-      </c>
-      <c r="O13">
-        <v>4</v>
-      </c>
-      <c r="P13">
-        <v>64</v>
-      </c>
-      <c r="Q13">
-        <v>2</v>
-      </c>
-      <c r="R13">
-        <v>4</v>
-      </c>
-      <c r="S13">
-        <v>65</v>
-      </c>
-      <c r="T13">
-        <v>2</v>
-      </c>
-      <c r="U13">
-        <v>4</v>
-      </c>
-      <c r="V13">
-        <v>66</v>
-      </c>
-      <c r="W13">
-        <v>2</v>
-      </c>
-      <c r="X13">
-        <v>2</v>
-      </c>
-      <c r="Y13">
-        <v>67</v>
-      </c>
-      <c r="Z13">
-        <v>2</v>
-      </c>
-      <c r="AA13">
-        <v>2</v>
-      </c>
-      <c r="AB13">
-        <v>68</v>
-      </c>
-      <c r="AC13">
-        <v>2</v>
-      </c>
-      <c r="AD13">
-        <v>2</v>
-      </c>
-      <c r="AE13">
-        <v>69</v>
-      </c>
-      <c r="AF13">
-        <v>2</v>
-      </c>
-      <c r="AG13">
-        <v>2</v>
-      </c>
-      <c r="AH13">
-        <v>70</v>
-      </c>
-      <c r="AI13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14">
-        <v>21</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>48</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
-      </c>
-      <c r="F14">
-        <v>4</v>
-      </c>
-      <c r="G14">
-        <v>49</v>
-      </c>
-      <c r="H14">
-        <v>4</v>
-      </c>
-      <c r="I14">
-        <v>4</v>
-      </c>
-      <c r="J14">
-        <v>50</v>
-      </c>
-      <c r="K14">
-        <v>4</v>
-      </c>
-      <c r="L14">
-        <v>4</v>
-      </c>
-      <c r="M14">
-        <v>51</v>
-      </c>
-      <c r="N14">
-        <v>4</v>
-      </c>
-      <c r="O14">
-        <v>4</v>
-      </c>
-      <c r="P14">
-        <v>52</v>
-      </c>
-      <c r="Q14">
-        <v>4</v>
-      </c>
-      <c r="R14">
-        <v>4</v>
-      </c>
-      <c r="S14">
-        <v>53</v>
-      </c>
-      <c r="T14">
-        <v>4</v>
-      </c>
-      <c r="U14">
-        <v>4</v>
-      </c>
-      <c r="V14">
-        <v>54</v>
-      </c>
-      <c r="W14">
-        <v>4</v>
-      </c>
-      <c r="X14">
-        <v>3</v>
-      </c>
-      <c r="Y14">
-        <v>55</v>
-      </c>
-      <c r="Z14">
-        <v>3</v>
-      </c>
-      <c r="AA14">
-        <v>3</v>
-      </c>
-      <c r="AB14">
-        <v>56</v>
-      </c>
-      <c r="AC14">
-        <v>3</v>
-      </c>
-      <c r="AD14">
-        <v>3</v>
-      </c>
-      <c r="AE14">
-        <v>57</v>
-      </c>
-      <c r="AF14">
-        <v>3</v>
-      </c>
-      <c r="AG14">
-        <v>3</v>
-      </c>
-      <c r="AH14">
-        <v>58</v>
-      </c>
-      <c r="AI14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>32</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15">
-        <v>3</v>
-      </c>
-      <c r="G15">
-        <v>15</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-      <c r="I15">
-        <v>3</v>
-      </c>
-      <c r="J15">
-        <v>32</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="L15">
-        <v>3</v>
-      </c>
-      <c r="M15">
-        <v>15</v>
-      </c>
-      <c r="N15">
-        <v>2</v>
-      </c>
-      <c r="O15">
-        <v>3</v>
-      </c>
-      <c r="P15">
-        <v>32</v>
-      </c>
-      <c r="Q15">
-        <v>2</v>
-      </c>
-      <c r="R15">
-        <v>3</v>
-      </c>
-      <c r="S15">
-        <v>15</v>
-      </c>
-      <c r="T15">
-        <v>2</v>
-      </c>
-      <c r="U15">
-        <v>3</v>
-      </c>
-      <c r="V15">
-        <v>15</v>
-      </c>
-      <c r="W15">
-        <v>2</v>
-      </c>
-      <c r="X15">
-        <v>4</v>
-      </c>
-      <c r="Y15">
-        <v>32</v>
-      </c>
-      <c r="Z15">
-        <v>2</v>
-      </c>
-      <c r="AA15">
-        <v>4</v>
-      </c>
-      <c r="AB15">
-        <v>32</v>
-      </c>
-      <c r="AC15">
-        <v>2</v>
-      </c>
-      <c r="AD15">
-        <v>4</v>
-      </c>
-      <c r="AE15">
-        <v>32</v>
-      </c>
-      <c r="AF15">
-        <v>4</v>
-      </c>
-      <c r="AG15">
-        <v>4</v>
-      </c>
-      <c r="AH15">
-        <v>15</v>
-      </c>
-      <c r="AI15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16">
-        <v>23</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>82</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>82</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="J16">
-        <v>82</v>
-      </c>
-      <c r="K16">
-        <v>2</v>
-      </c>
-      <c r="L16">
-        <v>2</v>
-      </c>
-      <c r="M16">
-        <v>82</v>
-      </c>
-      <c r="N16">
-        <v>2</v>
-      </c>
-      <c r="O16">
-        <v>2</v>
-      </c>
-      <c r="P16">
-        <v>82</v>
-      </c>
-      <c r="Q16">
-        <v>2</v>
-      </c>
-      <c r="R16">
-        <v>2</v>
-      </c>
-      <c r="S16">
-        <v>82</v>
-      </c>
-      <c r="T16">
-        <v>2</v>
-      </c>
-      <c r="U16">
-        <v>2</v>
-      </c>
-      <c r="V16">
-        <v>82</v>
-      </c>
-      <c r="W16">
-        <v>2</v>
-      </c>
-      <c r="X16">
-        <v>2</v>
-      </c>
-      <c r="Y16">
-        <v>82</v>
-      </c>
-      <c r="Z16">
-        <v>2</v>
-      </c>
-      <c r="AA16">
-        <v>2</v>
-      </c>
-      <c r="AB16">
-        <v>82</v>
-      </c>
-      <c r="AC16">
-        <v>2</v>
-      </c>
-      <c r="AD16">
-        <v>2</v>
-      </c>
-      <c r="AE16">
-        <v>82</v>
-      </c>
-      <c r="AF16">
-        <v>2</v>
-      </c>
-      <c r="AG16">
-        <v>2</v>
-      </c>
-      <c r="AH16">
-        <v>82</v>
-      </c>
-      <c r="AI16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" t="s">
-        <v>7</v>
-      </c>
-      <c r="M21" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" t="s">
-        <v>7</v>
-      </c>
-      <c r="S21" t="s">
-        <v>23</v>
-      </c>
-      <c r="T21" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" t="s">
-        <v>4</v>
-      </c>
-      <c r="V21" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22">
         <v>4</v>
       </c>
       <c r="D22">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -2304,7 +2180,7 @@
         <v>4</v>
       </c>
       <c r="G22">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H22">
         <v>2</v>
@@ -2313,16 +2189,16 @@
         <v>4</v>
       </c>
       <c r="J22">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L22">
         <v>4</v>
       </c>
       <c r="M22">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -2331,149 +2207,149 @@
         <v>4</v>
       </c>
       <c r="P22">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="Q22">
         <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="T22">
         <v>2</v>
       </c>
       <c r="U22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="W22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H23">
         <v>2</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="N23">
         <v>2</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="Q23">
         <v>2</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>2</v>
       </c>
       <c r="U23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="W23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K24">
         <v>4</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N24">
         <v>2</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="Q24">
         <v>2</v>
@@ -2482,7 +2358,7 @@
         <v>5</v>
       </c>
       <c r="S24">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="T24">
         <v>2</v>
@@ -2491,517 +2367,375 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="W24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>23</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>28</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>2</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>17</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>33</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>41</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>3</v>
+      </c>
+      <c r="J26">
         <v>14</v>
       </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25">
+      <c r="K26">
+        <v>3</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26">
+        <v>14</v>
+      </c>
+      <c r="Q26">
+        <v>3</v>
+      </c>
+      <c r="R26">
+        <v>3</v>
+      </c>
+      <c r="S26">
+        <v>41</v>
+      </c>
+      <c r="T26">
+        <v>3</v>
+      </c>
+      <c r="U26">
+        <v>3</v>
+      </c>
+      <c r="V26" t="s">
+        <v>18</v>
+      </c>
+      <c r="W26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>18</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>30</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>22</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27">
+        <v>30</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>3</v>
+      </c>
+      <c r="P27">
+        <v>22</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
+      </c>
+      <c r="S27">
+        <v>22</v>
+      </c>
+      <c r="T27">
+        <v>3</v>
+      </c>
+      <c r="U27">
+        <v>3</v>
+      </c>
+      <c r="V27">
+        <v>30</v>
+      </c>
+      <c r="W27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>19</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>24</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>37</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28">
+        <v>37</v>
+      </c>
+      <c r="K28">
+        <v>3</v>
+      </c>
+      <c r="L28">
+        <v>3</v>
+      </c>
+      <c r="M28">
+        <v>24</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28">
+        <v>3</v>
+      </c>
+      <c r="P28">
+        <v>37</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+      <c r="R28">
+        <v>3</v>
+      </c>
+      <c r="S28">
+        <v>24</v>
+      </c>
+      <c r="T28">
+        <v>3</v>
+      </c>
+      <c r="U28">
+        <v>3</v>
+      </c>
+      <c r="V28">
+        <v>24</v>
+      </c>
+      <c r="W28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>20</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
         <v>33</v>
       </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>41</v>
-      </c>
-      <c r="H25">
-        <v>2</v>
-      </c>
-      <c r="I25">
-        <v>4</v>
-      </c>
-      <c r="J25">
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>40</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29">
         <v>14</v>
       </c>
-      <c r="K25">
-        <v>4</v>
-      </c>
-      <c r="L25">
-        <v>4</v>
-      </c>
-      <c r="M25">
-        <v>16</v>
-      </c>
-      <c r="N25">
-        <v>2</v>
-      </c>
-      <c r="O25">
-        <v>4</v>
-      </c>
-      <c r="P25">
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+      <c r="M29" t="s">
+        <v>18</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29">
         <v>14</v>
       </c>
-      <c r="Q25">
-        <v>2</v>
-      </c>
-      <c r="R25">
-        <v>5</v>
-      </c>
-      <c r="S25">
-        <v>41</v>
-      </c>
-      <c r="T25">
-        <v>2</v>
-      </c>
-      <c r="U25">
-        <v>5</v>
-      </c>
-      <c r="V25">
-        <v>16</v>
-      </c>
-      <c r="W25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>3</v>
-      </c>
-      <c r="B26">
-        <v>15</v>
-      </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26">
-        <v>17</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26">
-        <v>4</v>
-      </c>
-      <c r="G26">
-        <v>17</v>
-      </c>
-      <c r="H26">
-        <v>2</v>
-      </c>
-      <c r="I26">
-        <v>4</v>
-      </c>
-      <c r="J26">
-        <v>17</v>
-      </c>
-      <c r="K26">
-        <v>4</v>
-      </c>
-      <c r="L26">
-        <v>4</v>
-      </c>
-      <c r="M26">
-        <v>24</v>
-      </c>
-      <c r="N26">
-        <v>2</v>
-      </c>
-      <c r="O26">
-        <v>4</v>
-      </c>
-      <c r="P26">
-        <v>37</v>
-      </c>
-      <c r="Q26">
-        <v>2</v>
-      </c>
-      <c r="R26">
-        <v>5</v>
-      </c>
-      <c r="S26">
-        <v>24</v>
-      </c>
-      <c r="T26">
-        <v>2</v>
-      </c>
-      <c r="U26">
-        <v>5</v>
-      </c>
-      <c r="V26">
-        <v>37</v>
-      </c>
-      <c r="W26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>3</v>
-      </c>
-      <c r="B27">
-        <v>16</v>
-      </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>11</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="F27">
-        <v>3</v>
-      </c>
-      <c r="G27">
-        <v>25</v>
-      </c>
-      <c r="H27">
-        <v>2</v>
-      </c>
-      <c r="I27">
-        <v>3</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>3</v>
-      </c>
-      <c r="L27">
-        <v>3</v>
-      </c>
-      <c r="M27">
-        <v>11</v>
-      </c>
-      <c r="N27">
-        <v>2</v>
-      </c>
-      <c r="O27">
-        <v>3</v>
-      </c>
-      <c r="P27">
-        <v>25</v>
-      </c>
-      <c r="Q27">
-        <v>2</v>
-      </c>
-      <c r="R27">
-        <v>5</v>
-      </c>
-      <c r="S27">
-        <v>11</v>
-      </c>
-      <c r="T27">
-        <v>2</v>
-      </c>
-      <c r="U27">
-        <v>5</v>
-      </c>
-      <c r="V27">
-        <v>25</v>
-      </c>
-      <c r="W27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>3</v>
-      </c>
-      <c r="B28">
-        <v>17</v>
-      </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>9</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28">
-        <v>3</v>
-      </c>
-      <c r="G28">
-        <v>9</v>
-      </c>
-      <c r="H28">
-        <v>2</v>
-      </c>
-      <c r="I28">
-        <v>3</v>
-      </c>
-      <c r="J28">
-        <v>9</v>
-      </c>
-      <c r="K28">
-        <v>3</v>
-      </c>
-      <c r="L28">
-        <v>3</v>
-      </c>
-      <c r="M28">
-        <v>21</v>
-      </c>
-      <c r="N28">
-        <v>2</v>
-      </c>
-      <c r="O28">
-        <v>3</v>
-      </c>
-      <c r="P28">
-        <v>21</v>
-      </c>
-      <c r="Q28">
-        <v>2</v>
-      </c>
-      <c r="R28">
-        <v>5</v>
-      </c>
-      <c r="S28">
-        <v>9</v>
-      </c>
-      <c r="T28">
-        <v>2</v>
-      </c>
-      <c r="U28">
-        <v>5</v>
-      </c>
-      <c r="V28">
-        <v>21</v>
-      </c>
-      <c r="W28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>3</v>
-      </c>
-      <c r="B29">
-        <v>21</v>
-      </c>
-      <c r="C29">
-        <v>10</v>
-      </c>
-      <c r="D29">
-        <v>44</v>
-      </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29">
-        <v>10</v>
-      </c>
-      <c r="G29">
-        <v>45</v>
-      </c>
-      <c r="H29">
-        <v>4</v>
-      </c>
-      <c r="I29">
-        <v>10</v>
-      </c>
-      <c r="J29">
-        <v>45</v>
-      </c>
-      <c r="K29">
-        <v>4</v>
-      </c>
-      <c r="L29">
-        <v>10</v>
-      </c>
-      <c r="M29">
-        <v>46</v>
-      </c>
-      <c r="N29">
-        <v>4</v>
-      </c>
-      <c r="O29">
-        <v>10</v>
-      </c>
-      <c r="P29">
-        <v>46</v>
-      </c>
       <c r="Q29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="T29">
         <v>2</v>
       </c>
       <c r="U29">
-        <v>4</v>
-      </c>
-      <c r="V29">
-        <v>47</v>
+        <v>2</v>
+      </c>
+      <c r="V29" t="s">
+        <v>18</v>
       </c>
       <c r="W29">
         <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>3</v>
-      </c>
-      <c r="B30">
-        <v>22</v>
-      </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-      <c r="D30">
-        <v>30</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>4</v>
-      </c>
-      <c r="G30">
-        <v>30</v>
-      </c>
-      <c r="H30">
-        <v>2</v>
-      </c>
-      <c r="I30">
-        <v>4</v>
-      </c>
-      <c r="J30">
-        <v>18</v>
-      </c>
-      <c r="K30">
-        <v>4</v>
-      </c>
-      <c r="L30">
-        <v>4</v>
-      </c>
-      <c r="M30">
-        <v>30</v>
-      </c>
-      <c r="N30">
-        <v>2</v>
-      </c>
-      <c r="O30">
-        <v>4</v>
-      </c>
-      <c r="P30">
-        <v>22</v>
-      </c>
-      <c r="Q30">
-        <v>2</v>
-      </c>
-      <c r="R30">
-        <v>5</v>
-      </c>
-      <c r="S30">
-        <v>22</v>
-      </c>
-      <c r="T30">
-        <v>2</v>
-      </c>
-      <c r="U30">
-        <v>5</v>
-      </c>
-      <c r="V30">
-        <v>22</v>
-      </c>
-      <c r="W30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>3</v>
-      </c>
-      <c r="B31">
-        <v>7</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>23</v>
-      </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
-      <c r="F31">
-        <v>2</v>
-      </c>
-      <c r="G31">
-        <v>28</v>
-      </c>
-      <c r="H31">
-        <v>2</v>
-      </c>
-      <c r="I31">
-        <v>2</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>2</v>
-      </c>
-      <c r="L31">
-        <v>2</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-      <c r="N31">
-        <v>2</v>
-      </c>
-      <c r="O31">
-        <v>2</v>
-      </c>
-      <c r="P31">
-        <v>1</v>
-      </c>
-      <c r="Q31">
-        <v>2</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
     <mergeCell ref="X1:Z1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:T17"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
@@ -3010,7 +2744,7 @@
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="AD1:AF1"/>
     <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="U17:W17"/>
     <mergeCell ref="U1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
+++ b/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\OneDrive\Desktop\Timetable\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2918608-FAE1-48A9-97E2-3325D22D4987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3F7FE1-F0AD-4AE2-A892-095831FE1093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -469,44 +469,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F52D849-8006-48A0-8D6B-88427B4C70FA}">
   <dimension ref="A1:AI29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" customWidth="1"/>
-    <col min="5" max="5" width="22.36328125" customWidth="1"/>
-    <col min="6" max="6" width="14.90625" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" customWidth="1"/>
-    <col min="8" max="8" width="19.1796875" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" customWidth="1"/>
-    <col min="10" max="10" width="12.08984375" customWidth="1"/>
-    <col min="11" max="11" width="19.1796875" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" customWidth="1"/>
-    <col min="13" max="13" width="10.90625" customWidth="1"/>
-    <col min="14" max="14" width="19.1796875" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" customWidth="1"/>
-    <col min="17" max="17" width="18.81640625" customWidth="1"/>
-    <col min="18" max="18" width="12.6328125" customWidth="1"/>
-    <col min="19" max="19" width="10.6328125" customWidth="1"/>
-    <col min="20" max="20" width="18.90625" customWidth="1"/>
-    <col min="21" max="21" width="12.6328125" customWidth="1"/>
-    <col min="22" max="22" width="10.54296875" customWidth="1"/>
-    <col min="23" max="23" width="17.90625" customWidth="1"/>
-    <col min="24" max="24" width="12.453125" customWidth="1"/>
-    <col min="25" max="25" width="11.90625" customWidth="1"/>
-    <col min="26" max="26" width="18.453125" customWidth="1"/>
-    <col min="27" max="27" width="13.08984375" customWidth="1"/>
-    <col min="28" max="28" width="11.08984375" customWidth="1"/>
-    <col min="29" max="29" width="18.08984375" customWidth="1"/>
-    <col min="30" max="30" width="12.90625" customWidth="1"/>
-    <col min="31" max="31" width="10.81640625" customWidth="1"/>
-    <col min="32" max="32" width="18.453125" customWidth="1"/>
-    <col min="33" max="33" width="13.54296875" customWidth="1"/>
-    <col min="34" max="34" width="10.90625" customWidth="1"/>
-    <col min="35" max="35" width="18.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" customWidth="1"/>
+    <col min="11" max="11" width="19.21875" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" customWidth="1"/>
+    <col min="13" max="13" width="10.88671875" customWidth="1"/>
+    <col min="14" max="14" width="19.21875" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" customWidth="1"/>
+    <col min="17" max="17" width="18.77734375" customWidth="1"/>
+    <col min="18" max="18" width="12.6640625" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" customWidth="1"/>
+    <col min="20" max="20" width="18.88671875" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" customWidth="1"/>
+    <col min="22" max="22" width="10.5546875" customWidth="1"/>
+    <col min="23" max="23" width="17.88671875" customWidth="1"/>
+    <col min="24" max="24" width="12.44140625" customWidth="1"/>
+    <col min="25" max="25" width="11.88671875" customWidth="1"/>
+    <col min="26" max="26" width="18.44140625" customWidth="1"/>
+    <col min="27" max="27" width="13.109375" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" customWidth="1"/>
+    <col min="29" max="29" width="18.109375" customWidth="1"/>
+    <col min="30" max="30" width="12.88671875" customWidth="1"/>
+    <col min="31" max="31" width="10.77734375" customWidth="1"/>
+    <col min="32" max="32" width="18.44140625" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" customWidth="1"/>
+    <col min="34" max="34" width="10.88671875" customWidth="1"/>
+    <col min="35" max="35" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -569,7 +569,7 @@
       <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" t="s">
@@ -672,7 +672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -779,7 +779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -886,7 +886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
@@ -1880,7 +1880,7 @@
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" t="s">
@@ -1947,7 +1947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>2</v>
       </c>
       <c r="G29">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -2680,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="J29">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K29">
         <v>2</v>
@@ -2724,6 +2724,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="U1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A17:A18"/>
@@ -2740,12 +2746,6 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="U1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
+++ b/TIME TABLE SAMPLE DATA/UPDATED TIMETABLE TOTAL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\OneDrive\Desktop\Timetable\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3F7FE1-F0AD-4AE2-A892-095831FE1093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{8B3F7FE1-F0AD-4AE2-A892-095831FE1093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1A23A6B-A519-49A1-AE67-5BFBFFB02B65}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA5131F-FD47-46FE-8D38-CE3A574D862A}"/>
   </bookViews>
@@ -1183,7 +1183,7 @@
         <v>2</v>
       </c>
       <c r="AB7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -1735,7 +1735,7 @@
         <v>2</v>
       </c>
       <c r="B13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -2724,12 +2724,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="U1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A17:A18"/>
@@ -2746,6 +2740,12 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="U1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
